--- a/artfynd/A 28464-2025 artfynd.xlsx
+++ b/artfynd/A 28464-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>126803537</v>
       </c>
       <c r="B3" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126803535</v>
       </c>
       <c r="B4" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126803536</v>
       </c>
       <c r="B5" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>126803538</v>
       </c>
       <c r="B6" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>126806740</v>
       </c>
       <c r="B7" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28464-2025 artfynd.xlsx
+++ b/artfynd/A 28464-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>126803537</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126803535</v>
       </c>
       <c r="B4" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126803536</v>
       </c>
       <c r="B5" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>126803538</v>
       </c>
       <c r="B6" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>126806740</v>
       </c>
       <c r="B7" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28464-2025 artfynd.xlsx
+++ b/artfynd/A 28464-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>126803537</v>
       </c>
       <c r="B3" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126803535</v>
       </c>
       <c r="B4" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126803536</v>
       </c>
       <c r="B5" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>126803538</v>
       </c>
       <c r="B6" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>126806740</v>
       </c>
       <c r="B7" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28464-2025 artfynd.xlsx
+++ b/artfynd/A 28464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126803533</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>126803537</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>126803535</v>
       </c>
       <c r="B4" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126803536</v>
       </c>
       <c r="B5" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>126803538</v>
       </c>
       <c r="B6" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>126806740</v>
       </c>
       <c r="B7" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 28464-2025 artfynd.xlsx
+++ b/artfynd/A 28464-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126803533</v>
+        <v>126803532</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandmon, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529301</v>
+        <v>529302</v>
       </c>
       <c r="R2" t="n">
-        <v>6501476</v>
+        <v>6501539</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -784,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126803537</v>
+        <v>126803535</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529334</v>
+        <v>529335</v>
       </c>
       <c r="R3" t="n">
-        <v>6501401</v>
+        <v>6501387</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -881,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126803535</v>
+        <v>126803536</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529335</v>
+        <v>529340</v>
       </c>
       <c r="R4" t="n">
-        <v>6501387</v>
+        <v>6501417</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -978,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126803536</v>
+        <v>126803537</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529340</v>
+        <v>529334</v>
       </c>
       <c r="R5" t="n">
-        <v>6501417</v>
+        <v>6501401</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1078,7 +1066,7 @@
         <v>126803538</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1163,7 @@
         <v>126806740</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,6 +1259,115 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126803533</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sandmon, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>529301</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6501476</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällestad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28464-2025 artfynd.xlsx
+++ b/artfynd/A 28464-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126803532</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126803535</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126803536</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126803537</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126803538</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126806740</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,8 +1402,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126803533</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>